--- a/src/microservices/thirdParties/static/Plantilla_Registro_Rutas_de_Transporte .xlsx
+++ b/src/microservices/thirdParties/static/Plantilla_Registro_Rutas_de_Transporte .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\cali-mobility\cali-mobility-backend\src\microservices\thirdParties\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EFF845-936E-4165-AF9F-F1AA2F92060B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A3BA72-9936-405A-8B68-5CA084CA71F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -510,7 +510,55 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{0B78AF42-D19D-42D6-889A-7DD61D565F2C}">
+    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{9CE66F0F-D647-4FE8-AF45-64E255444AD7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+El origen y destino deberian ser diferentes</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{704DC735-5ACE-46F9-A508-D6C3575D9CB9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+El origen y destino deberian ser diferentes</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{0B78AF42-D19D-42D6-889A-7DD61D565F2C}">
       <text>
         <r>
           <rPr>
@@ -534,7 +582,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{47EEBA9B-5877-40F4-8719-0867CD8C4E91}">
+    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{47EEBA9B-5877-40F4-8719-0867CD8C4E91}">
       <text>
         <r>
           <rPr>
@@ -558,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{A8DD256A-7B6B-4F6E-9DF5-EA3462B3F76E}">
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{A8DD256A-7B6B-4F6E-9DF5-EA3462B3F76E}">
       <text>
         <r>
           <rPr>
@@ -582,7 +630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{3F1B0684-A3AA-45F3-8E74-CCD979FDEC6F}">
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{3F1B0684-A3AA-45F3-8E74-CCD979FDEC6F}">
       <text>
         <r>
           <rPr>
@@ -611,7 +659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="35">
   <si>
     <t>20:00</t>
   </si>
@@ -800,7 +848,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,6 +1009,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1692,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463ECA68-AF7C-434F-984C-DDAF296BE286}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" style="2" customWidth="1"/>
@@ -2004,11 +2065,11 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
@@ -2017,7 +2078,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>12</v>
@@ -2025,10 +2086,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
@@ -2037,15 +2098,15 @@
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>28</v>
+      <c r="A18" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
@@ -2057,7 +2118,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>12</v>
@@ -2065,21 +2126,41 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>27</v>
       </c>
     </row>
